--- a/sample_master.xlsx
+++ b/sample_master.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Company</t>
   </si>
@@ -56,10 +56,22 @@
     <t>John Smith</t>
   </si>
   <si>
+    <t>Coordinator1</t>
+  </si>
+  <si>
     <t>Task</t>
   </si>
   <si>
     <t>Firmware update</t>
+  </si>
+  <si>
+    <t>F/W Update</t>
+  </si>
+  <si>
+    <t>Firm ware update</t>
+  </si>
+  <si>
+    <t>Commissioning</t>
   </si>
   <si>
     <t>Inspection</t>
@@ -472,7 +484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -520,6 +532,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -527,27 +544,42 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -562,27 +594,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -597,17 +629,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
